--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailImportError.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationDetailImportError.xlsx
@@ -302,7 +302,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.000000_ "/>
   </numFmts>
   <fonts count="21">
